--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64995_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64995_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5121862791224eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R89d81195669c4d5b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,66 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.2975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.8364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.2195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.5888</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.9688</x:v>
+        <x:v>     74.4209</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64995_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64995_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R89d81195669c4d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0c2f28658a9d4f64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,741 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.5313</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.6514</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.0670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.7585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     98.8398</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.2975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.9790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.6806</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.2195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.6806</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.3754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.2195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.9416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.8456</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.7585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.2895</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.4501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.2975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.5930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.3399</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.5280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.2975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.7585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.8364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.8364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.2975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.8364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.2195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.9890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.8285</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.2975</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.5280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.1449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>18/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.2975</x:v>
+        <x:v>     79.3754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.5058</x:v>
+        <x:v>     83.9316</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.7025</x:v>
+        <x:v>     79.7139</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.4557</x:v>
+        <x:v>     75.4056</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.0464</x:v>
+        <x:v>    114.7190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    110.4063</x:v>
+        <x:v>    109.9706</x:v>
       </x:c>
     </x:row>
     <x:row>
